--- a/Documentos Base/Sprint 7 documentacion/Sprint_07_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 7 documentacion/Sprint_07_Backlog_ICARO.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 7 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE1377B-48E1-4AC7-BDDE-15CD2FB5E1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ABC906-B3E6-4B44-A49B-A01C02D3516A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
     <sheet name="RESUMEN DE VELOCIDAD" sheetId="3" r:id="rId2"/>
     <sheet name="Glosario" sheetId="5" r:id="rId3"/>
-    <sheet name="Resumen CP" sheetId="2" r:id="rId4"/>
+    <sheet name="Resumen Casos de Prueba" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1381,26 +1381,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1447,6 +1429,22 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1511,25 +1509,29 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1947,10 +1949,12 @@
   <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" style="7" customWidth="1"/>
     <col min="10" max="10" width="39.42578125" customWidth="1"/>
     <col min="11" max="11" width="40.5703125" customWidth="1"/>
     <col min="12" max="12" width="40.42578125" customWidth="1"/>
@@ -1989,7 +1993,7 @@
       <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="1" t="s">
         <v>182</v>
       </c>
       <c r="B3" s="26" t="s">
@@ -1999,7 +2003,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="1" t="s">
         <v>184</v>
       </c>
       <c r="H3" s="38" t="s">
@@ -2011,7 +2015,7 @@
       <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:12" ht="24">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B4" s="41">
@@ -2021,7 +2025,7 @@
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
       <c r="F4" s="28"/>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="1" t="s">
         <v>186</v>
       </c>
       <c r="H4" s="41">
@@ -2033,7 +2037,7 @@
       <c r="L4" s="28"/>
     </row>
     <row r="5" spans="1:12" ht="128.25" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="1" t="s">
         <v>187</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -2043,7 +2047,7 @@
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
       <c r="F5" s="25"/>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="1" t="s">
         <v>188</v>
       </c>
       <c r="H5" s="26" t="s">
@@ -2055,7 +2059,7 @@
       <c r="L5" s="28"/>
     </row>
     <row r="6" spans="1:12" ht="24">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -2065,7 +2069,7 @@
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="3" t="s">
         <v>190</v>
       </c>
       <c r="H6" s="32" t="s">
@@ -2077,304 +2081,304 @@
       <c r="L6" s="34"/>
     </row>
     <row r="7" spans="1:12" ht="30">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="4" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="185.25" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="6">
         <v>8</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="6">
         <v>8</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="229.5" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="6">
         <v>10</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="6">
         <v>10</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="5" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="198.75" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="6">
         <v>5</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="6">
         <v>5</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="5" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="274.5" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="6">
         <v>12</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="6">
         <v>12</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="226.5" customHeight="1">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="6">
         <v>8</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="6">
         <v>8</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="138" customHeight="1">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="6">
         <v>5</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="5" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49">
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="18">
         <v>48</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="18">
         <v>48</v>
       </c>
-      <c r="H14" s="50"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2400,198 +2404,198 @@
       <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="8" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="9">
         <v>48</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="9">
         <v>48</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="9" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="9">
         <v>5</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="9">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="9">
         <v>1</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="9">
         <v>1</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="9">
         <v>6</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="9">
         <v>6</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="9">
         <v>6</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="9">
         <v>6</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="9">
         <v>0</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="9">
         <v>0</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="9" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="9">
         <v>0</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="9">
         <v>0</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="9" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="9">
         <v>48</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="9">
         <v>48</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="10">
         <v>1</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="9">
         <v>46</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="9">
         <v>46</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="9" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="10">
         <v>1</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="11">
         <v>46179</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="11">
         <v>46179</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="9" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="9">
         <v>168</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="9">
         <v>168</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="9" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2619,182 +2623,182 @@
       <c r="A1" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="12" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="14" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="16" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="14" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="16" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="14" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="14" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="14" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="16" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -2811,960 +2815,960 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="1" max="2" width="10" style="53" customWidth="1"/>
+    <col min="3" max="3" width="20" style="53" customWidth="1"/>
+    <col min="4" max="4" width="75.85546875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="10" style="53" customWidth="1"/>
+    <col min="6" max="6" width="45" style="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="47" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="49" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="52" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="49" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="52" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="49" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="52" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="49" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="E10" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="52" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="E11" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="49" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="52" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="49" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="52" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="E15" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="49" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="52" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="49" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="52" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="49" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="52" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="49" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="52" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="E23" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="49" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="52" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="E25" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="49" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="6" t="s">
+      <c r="E27" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="49" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="52" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="49" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="52" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="E31" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="49" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="52" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="6" t="s">
+      <c r="E33" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="49" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="52" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="6" t="s">
+      <c r="E35" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="49" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="52" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="E37" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" s="49" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="E38" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="52" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="6" t="s">
+      <c r="E39" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="49" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="52" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" s="6" t="s">
+      <c r="E41" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="49" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="E42" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="52" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="6" t="s">
+      <c r="E43" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="49" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="52" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" s="6" t="s">
+      <c r="E45" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" s="49" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="52" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="49" t="s">
         <v>173</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47" s="6" t="s">
+      <c r="E47" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" s="49" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="E48" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="52" t="s">
         <v>177</v>
       </c>
     </row>
